--- a/Audit Guidelines with Possibility Column.xlsx
+++ b/Audit Guidelines with Possibility Column.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="130" yWindow="550" windowWidth="18880" windowHeight="8740" activeTab="1"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Audit Guidelines with Possibili" sheetId="1" r:id="rId5"/>
+    <sheet name="Audit Guidelines with Possibili" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="283">
   <si>
     <t>ID</t>
   </si>
@@ -665,23 +669,619 @@
   </si>
   <si>
     <t>Possibility: Discharge note says "Patient to return next week for Cycle 2 Chemo." This is a planned readmission, not a failure.</t>
+  </si>
+  <si>
+    <t>Excisional Debridement</t>
+  </si>
+  <si>
+    <t>463, 464, 465</t>
+  </si>
+  <si>
+    <r>
+      <t>99231</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Low MDM)</t>
+    </r>
+  </si>
+  <si>
+    <t>TAVR Approach</t>
+  </si>
+  <si>
+    <t>216–221</t>
+  </si>
+  <si>
+    <r>
+      <t>33361</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (TAVR)</t>
+    </r>
+  </si>
+  <si>
+    <t>Spinal Fusion</t>
+  </si>
+  <si>
+    <t>453, 454, 455</t>
+  </si>
+  <si>
+    <r>
+      <t>63047</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Decompress)</t>
+    </r>
+  </si>
+  <si>
+    <t>Hip Fracture ORIF</t>
+  </si>
+  <si>
+    <t>521, 522</t>
+  </si>
+  <si>
+    <t>96+ Hour Vent</t>
+  </si>
+  <si>
+    <r>
+      <t>99291</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Crit. Care)</t>
+    </r>
+  </si>
+  <si>
+    <t>981, 982, 983</t>
+  </si>
+  <si>
+    <t>619, 620, 621</t>
+  </si>
+  <si>
+    <r>
+      <t>43775</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Sleeve)</t>
+    </r>
+  </si>
+  <si>
+    <t>308, 309, 310</t>
+  </si>
+  <si>
+    <r>
+      <t>60220</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Partial)</t>
+    </r>
+  </si>
+  <si>
+    <t>Audit Concept</t>
+  </si>
+  <si>
+    <t>Target MS-DRG</t>
+  </si>
+  <si>
+    <t>Primary ICD-10-PCS (Facility)</t>
+  </si>
+  <si>
+    <t>Professional CPT (The "Truth" Trigger)</t>
+  </si>
+  <si>
+    <t>Specific Logic Filter (SQL/Python Logic)</t>
+  </si>
+  <si>
+    <t>SME Clinical Logic &amp; Edge Cases</t>
+  </si>
+  <si>
+    <r>
+      <t>0JBN0ZZ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Subcut/Fascia)</t>
+    </r>
+  </si>
+  <si>
+    <t>DRG IN (463-465) AND LOS &lt; 2 AND Prof_CPT = 99231 AND NO CPT 11042</t>
+  </si>
+  <si>
+    <r>
+      <t>Negative:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If the doctor bills a low-level visit (99231) and no excisional CPT, the "0JBN" is likely just wound cleaning.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>02RF0ZZ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Open Aortic)</t>
+    </r>
+  </si>
+  <si>
+    <t>DRG IN (216-221) AND Proc = '02RF0ZZ' AND Prof_CPT = 33361</t>
+  </si>
+  <si>
+    <r>
+      <t>Positive:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> CPT 33361 is strictly percutaneous. It physically contradicts the "0" (Open) approach in the 5th char of the PCS code.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>0RG107Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Fusion)</t>
+    </r>
+  </si>
+  <si>
+    <t>DRG IN (453-455) AND Prof_CPT = 63047 AND Prof_CPT NOT LIKE '22%'</t>
+  </si>
+  <si>
+    <r>
+      <t>Negative:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If the surgeon bills only 63047 (Laminectomy) and no 22xxx (Fusion) codes, the "0RG1" facility code is unsupported.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5A1955Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (&gt;96 hrs)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DRG = '003' AND LOS &lt; 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (OR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Units of 99291 &lt; 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Hard Error:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A patient cannot have 96 hours of ventilation in a stay lasting only 48-72 hours. This is a "hard fail" audit.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>0SR90JZ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Replacement)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>27244</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (ORIF)</t>
+    </r>
+  </si>
+  <si>
+    <t>DRG IN (521, 522) AND Prof_CPT = 27244 AND DX LIKE 'S72%'</t>
+  </si>
+  <si>
+    <r>
+      <t>Positive:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Facility billed for a full joint replacement (0SR9), but surgeon billed for internal fixation (screws/nails).</t>
+    </r>
+  </si>
+  <si>
+    <t>Unrelated O.R. (981)</t>
+  </si>
+  <si>
+    <t>Any Major PCS</t>
+  </si>
+  <si>
+    <r>
+      <t>99223</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Initial DX)</t>
+    </r>
+  </si>
+  <si>
+    <t>DRG = 981 AND MDC_Proc != MDC_PDX AND CPT_PDX = Proc_MDC_DX</t>
+  </si>
+  <si>
+    <r>
+      <t>Positive:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If the MD's initial diagnosis (99223) matches the surgery, the facility mis-sequenced the PDX, triggering the high-cost 981 bucket.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bariatric Upcode</t>
+  </si>
+  <si>
+    <r>
+      <t>0D163ZA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Bypass)</t>
+    </r>
+  </si>
+  <si>
+    <t>DRG IN (619-621) AND Proc = '0D163ZA' AND Prof_CPT = 43775</t>
+  </si>
+  <si>
+    <r>
+      <t>Negative:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Sleeve Gastrectomy (43775) is lower risk. Facility upcoding to Bypass (0D163ZA) yields a $5k+ overpayment.</t>
+    </r>
+  </si>
+  <si>
+    <t>Shoulder Revision</t>
+  </si>
+  <si>
+    <t>483, 484</t>
+  </si>
+  <si>
+    <r>
+      <t>0RRJ0JZ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Total)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>23470</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Hemi)</t>
+    </r>
+  </si>
+  <si>
+    <t>DRG IN (483, 484) AND Prof_CPT = 23470</t>
+  </si>
+  <si>
+    <r>
+      <t>Negative:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Surgeon billed for a partial/hemi (23470), but facility coded a total replacement (0RRJ). Check implant logs for verification.</t>
+    </r>
+  </si>
+  <si>
+    <t>Pacemaker System</t>
+  </si>
+  <si>
+    <t>242, 243, 244</t>
+  </si>
+  <si>
+    <r>
+      <t>0JH604Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Insertion)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>33222</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Pocket only)</t>
+    </r>
+  </si>
+  <si>
+    <t>DRG IN (242-244) AND Prof_CPT = 33222</t>
+  </si>
+  <si>
+    <r>
+      <t>Negative:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Facility billed for a new system insertion (0JH6), but surgeon only billed for a pocket revision (33222).</t>
+    </r>
+  </si>
+  <si>
+    <t>Thyroid Total</t>
+  </si>
+  <si>
+    <r>
+      <t>0GBK0ZZ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Total)</t>
+    </r>
+  </si>
+  <si>
+    <t>DRG IN (308-310) AND Proc = '0GBK0ZZ' AND Prof_CPT = 60220</t>
+  </si>
+  <si>
+    <r>
+      <t>Negative:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Surgeon and Path-report confirm only one lobe was removed. Facility upcoded to "Total" to hit a higher DRG.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="5">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF444746"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -689,40 +1289,64 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -912,17 +1536,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -942,9 +1569,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -962,9 +1589,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -982,9 +1609,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
       <c r="A4" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
@@ -1002,9 +1629,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
@@ -1022,9 +1649,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
@@ -1042,9 +1669,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
@@ -1062,9 +1689,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
       <c r="A8" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
@@ -1082,9 +1709,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
       <c r="A9" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
@@ -1102,9 +1729,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
       <c r="A10" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
@@ -1122,9 +1749,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>43</v>
@@ -1142,9 +1769,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1">
       <c r="A12" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>43</v>
@@ -1162,9 +1789,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" ht="15.75" customHeight="1">
       <c r="A13" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>43</v>
@@ -1182,9 +1809,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
       <c r="A14" s="1">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>43</v>
@@ -1202,9 +1829,9 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="A15" s="1">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>43</v>
@@ -1222,9 +1849,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1">
       <c r="A16" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>64</v>
@@ -1242,9 +1869,9 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="1">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>64</v>
@@ -1262,9 +1889,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>64</v>
@@ -1282,9 +1909,9 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1">
       <c r="A19" s="1">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>64</v>
@@ -1302,9 +1929,9 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="1">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>64</v>
@@ -1322,9 +1949,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1">
       <c r="A21" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>85</v>
@@ -1342,9 +1969,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" ht="12.5">
       <c r="A22" s="1">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>85</v>
@@ -1362,9 +1989,9 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" ht="12.5">
       <c r="A23" s="1">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>85</v>
@@ -1382,9 +2009,9 @@
         <v>97</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" ht="12.5">
       <c r="A24" s="1">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>85</v>
@@ -1402,9 +2029,9 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" ht="12.5">
       <c r="A25" s="1">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>85</v>
@@ -1422,9 +2049,9 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" ht="12.5">
       <c r="A26" s="1">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>106</v>
@@ -1442,9 +2069,9 @@
         <v>110</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" ht="12.5">
       <c r="A27" s="1">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>106</v>
@@ -1462,9 +2089,9 @@
         <v>114</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" ht="12.5">
       <c r="A28" s="1">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>106</v>
@@ -1482,9 +2109,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" ht="12.5">
       <c r="A29" s="1">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>119</v>
@@ -1502,9 +2129,9 @@
         <v>123</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:6" ht="12.5">
       <c r="A30" s="1">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>119</v>
@@ -1522,9 +2149,9 @@
         <v>127</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:6" ht="12.5">
       <c r="A31" s="1">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>128</v>
@@ -1542,9 +2169,9 @@
         <v>132</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:6" ht="12.5">
       <c r="A32" s="1">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>128</v>
@@ -1562,9 +2189,9 @@
         <v>136</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:6" ht="12.5">
       <c r="A33" s="1">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>128</v>
@@ -1582,9 +2209,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:6" ht="12.5">
       <c r="A34" s="1">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>128</v>
@@ -1602,9 +2229,9 @@
         <v>144</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:6" ht="12.5">
       <c r="A35" s="1">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>128</v>
@@ -1622,9 +2249,9 @@
         <v>148</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:6" ht="12.5">
       <c r="A36" s="1">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>149</v>
@@ -1642,9 +2269,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:6" ht="12.5">
       <c r="A37" s="1">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>149</v>
@@ -1662,9 +2289,9 @@
         <v>157</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:6" ht="12.5">
       <c r="A38" s="1">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>149</v>
@@ -1682,9 +2309,9 @@
         <v>161</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:6" ht="12.5">
       <c r="A39" s="1">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>162</v>
@@ -1702,9 +2329,9 @@
         <v>166</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:6" ht="12.5">
       <c r="A40" s="1">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>167</v>
@@ -1722,9 +2349,9 @@
         <v>171</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:6" ht="12.5">
       <c r="A41" s="1">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>167</v>
@@ -1742,9 +2369,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:6" ht="12.5">
       <c r="A42" s="1">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>167</v>
@@ -1762,9 +2389,9 @@
         <v>179</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:6" ht="12.5">
       <c r="A43" s="1">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>167</v>
@@ -1782,9 +2409,9 @@
         <v>183</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:6" ht="12.5">
       <c r="A44" s="1">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>167</v>
@@ -1802,9 +2429,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:6" ht="12.5">
       <c r="A45" s="1">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>167</v>
@@ -1822,9 +2449,9 @@
         <v>191</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:6" ht="12.5">
       <c r="A46" s="1">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>167</v>
@@ -1842,9 +2469,9 @@
         <v>195</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:6" ht="12.5">
       <c r="A47" s="1">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>167</v>
@@ -1862,9 +2489,9 @@
         <v>199</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:6" ht="12.5">
       <c r="A48" s="1">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>200</v>
@@ -1882,9 +2509,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:6" ht="12.5">
       <c r="A49" s="1">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>200</v>
@@ -1902,9 +2529,9 @@
         <v>208</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:6" ht="12.5">
       <c r="A50" s="1">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>209</v>
@@ -1922,9 +2549,9 @@
         <v>213</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:6" ht="12.5">
       <c r="A51" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>209</v>
@@ -1943,6 +2570,237 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="78.5" thickBot="1">
+      <c r="A1" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="164" thickBot="1">
+      <c r="A2" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="188.5" thickBot="1">
+      <c r="A3" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="201.5" thickBot="1">
+      <c r="A4" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="176.5" thickBot="1">
+      <c r="A5" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B5" s="2">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="176" thickBot="1">
+      <c r="A6" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="238.5" thickBot="1">
+      <c r="A7" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="201.5" thickBot="1">
+      <c r="A8" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="239" thickBot="1">
+      <c r="A9" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="176.5" thickBot="1">
+      <c r="A10" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="176.5" thickBot="1">
+      <c r="A11" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>